--- a/TestData/TMTT0022150_VerificationOfCoverageCompanyDashboardNewUIAndFunctionality.xlsx
+++ b/TestData/TMTT0022150_VerificationOfCoverageCompanyDashboardNewUIAndFunctionality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C81073-7B93-4DD2-8A0E-687B9C15617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936F6AB9-224E-4361-B16F-BE98CD696A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,28 @@
     <sheet name="ActivityColumns" sheetId="4" r:id="rId5"/>
     <sheet name="Activity" sheetId="11" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Users</t>
   </si>
@@ -146,25 +157,34 @@
     <t>Test External</t>
   </si>
   <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Tier</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>Companies Discussed</t>
+  </si>
+  <si>
+    <t>External Contact Company</t>
+  </si>
+  <si>
+    <t>CapProviderTestCompany</t>
+  </si>
+  <si>
     <t>James Craven</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>..</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>Tier</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>StandardTestCompany</t>
+    <t>Indrajeet Singh</t>
   </si>
 </sst>
 </file>
@@ -494,20 +514,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K12">
+        <f>60+45</f>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -519,16 +548,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F6AD56-19A8-4526-A92B-5BB161C99B6D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -540,62 +569,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7972DAA3-2502-4122-BD46-655C1E9DC13D}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -609,42 +638,42 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F867BB15-8B6C-4F1B-B262-3A41B97B60E4}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -657,73 +686,83 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="19.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultColWidth="19.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -735,17 +774,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB9990D-2177-413E-8716-FEF5A04433C7}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
@@ -768,7 +807,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>

--- a/TestData/TMTT0022150_VerificationOfCoverageCompanyDashboardNewUIAndFunctionality.xlsx
+++ b/TestData/TMTT0022150_VerificationOfCoverageCompanyDashboardNewUIAndFunctionality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D67402-1842-4D98-A5BF-907FC6F240B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936F6AB9-224E-4361-B16F-BE98CD696A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="528" windowWidth="21384" windowHeight="10548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,28 @@
     <sheet name="ActivityColumns" sheetId="4" r:id="rId5"/>
     <sheet name="Activity" sheetId="11" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Users</t>
   </si>
@@ -171,6 +182,9 @@
   </si>
   <si>
     <t>James Craven</t>
+  </si>
+  <si>
+    <t>Indrajeet Singh</t>
   </si>
 </sst>
 </file>
@@ -500,20 +514,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K12">
+        <f>60+45</f>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -525,14 +548,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F6AD56-19A8-4526-A92B-5BB161C99B6D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -546,62 +569,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7972DAA3-2502-4122-BD46-655C1E9DC13D}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -615,42 +638,42 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F867BB15-8B6C-4F1B-B262-3A41B97B60E4}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -664,80 +687,80 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="19.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="19.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -751,17 +774,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB9990D-2177-413E-8716-FEF5A04433C7}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
@@ -784,7 +807,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
